--- a/test/standard_mapping/output_dpr_first100.xlsx
+++ b/test/standard_mapping/output_dpr_first100.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Program\VScode\workspace\data-governance\test\standard_mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{012E9190-A6D1-4C5E-8384-836A32666033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C7279E-1D02-4D3E-9892-DD38DABF71BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1187,9 +1187,6 @@
     <t>模板名称</t>
   </si>
   <si>
-    <t>先分析字段：名称'参数模板名称'，业务含义'通过参数模板管理功能，由维护人员填写的参数模板名称'，核心语义是参数模板的名称，属于'模板名称'大类下的参数模板细分。逐一分析备选：D00017912'模板名称'业务定义'短信、邮件等预定义固定格式模板的名称'，是通用模板名称概念，字段'参数模板'正是一种模板，语义同源但原定义仅列举短信、邮件模板，未明确覆盖参数模板；D00028451'参数名称'是参数本身的名称为便于参数管理设定，不包含'模板'概念；D00036116'应用模板名称'限定应用组件模板、D00028466'流程模板名称'限定流程模板，均为其他模板类型；D00034631'短信模板参数'、D00034086'JOB参数名'、D00085852'功能输入参数'等与模板名称概念不同。权衡：字段与D00017912'模板名称'语义同源，直接判定新增会丢弃已有标准，判定直接复用则原定义未显式覆盖参数模板；通过扩展定义将参数模板纳入'模板名称'覆盖范围，既复用标准又满足字段需要，故选择'复用已有标准但扩展业务定义'。 扩展建议: 短信、邮件、参数等预定义固定格式模板的名称，包括通过参数模板管理功能由维护人员填写的参数模板名称</t>
-  </si>
-  <si>
     <t>D00036116 应用模板名称
 D00028451 参数名称
 D00087552 参数中文名称
@@ -1229,9 +1226,6 @@
     <t>参数编号</t>
   </si>
   <si>
-    <t>先分析字段：名称'参数表编号'，业务含义'通过参数模板管理功能，由维护人员填写的参数表编号'，数据示例'CS0001'，核心语义是参数体系中的编号，用于参数管理。逐一分析备选：D00028446'参数编号'业务定义'参数在使用过程中，为了便于参数管理，而设定的编号'，与字段'参数表编号'同属参数管理编号体系，语义最匹配，匹配度最高；D00029464'参考数据编号'、D00029580'上级参考数据编号'针对参考数据机制，与参数编号有差异；D00018195'客户参数编号'限定客户参考信息、D00034642'审核配置参数编号'限定审核配置、D00016051'SWIFT参数编号'、D00016815'联行号参数编号'、D00088531'余额核算参数编号'、D00017138'信息项统计参数编号'均为特定业务参数编号，范围窄于字段的通用参数表编号；D00001473'核算参数码'、D00001474'计息参数码'、D00050497'核查功能码'为参数码概念；其余为表单编号、报表编号、员工号等，与参数编号无关。权衡：D00028446'参数编号'的定义'为了便于参数管理而设定的编号'与字段的'参数表编号'语义一致，覆盖面合适，故选择复用D00028446，无需扩展。</t>
-  </si>
-  <si>
     <t>D00028446 参数编号
 D00029464 参考数据编号
 D00018195 客户参数编号
@@ -1266,9 +1260,6 @@
   </si>
   <si>
     <t>ECM文件编号</t>
-  </si>
-  <si>
-    <t>先分析字段：名称'文件编号（doc_id）'，业务含义'通过参数模板管理功能，上传模板到ECM后返回的doc_id字段'，数据示例'20260604603_30000277_01001'，核心语义是ECM系统中对上传文件生成的编号。逐一分析备选：D00027232'ECM文件编号'业务定义'ECM系统中对每个文件生成的编号，主要用来区分不同的文件'，与字段'上传模板到ECM后返回的doc_id'在系统场景与语义上完全对应，匹配度最高；D00012320'文件编号'是通用文件编号，虽名称与字段更接近但未体现ECM场景，精确度低于D00027232；D00021829'数据文件编号'限定传输数据文件、D00027874'文件组编号'限定文件组、D00027353'文件主编号'是上级编号、D00028906'文件夹编号'是目录编号、D00028454'错误文件编号'限定错误文件、D00047613'介绍信文件编号'、D00027887'GUOP文件编号'、D00028369'稿纸文件编号'、D00018422'银银平台文件编号'均为其他特定系统或场景的文件编号，与ECM场景不符。权衡：字段明确为ECM上传后返回的doc_id，D00027232的业务定义最精确地覆盖该场景，按'选择业务定义最精确、覆盖面最合适'的原则，选择复用D00027232，无需扩展。</t>
   </si>
   <si>
     <t>D00047613 介绍信文件编号
@@ -1400,9 +1391,6 @@
     <t>更新人员工号</t>
   </si>
   <si>
-    <t>先分析字段：名称'上传人工号'，业务含义'通过参数模板管理功能，维护模板，维护人员的工号'，核心语义是'维护模板人员的工号'。逐一分析备选：D00027859'更新人员工号'业务定义'表示维护相关记录的人员员工号信息'，与字段中'维护模板、维护人员'的语义高度吻合，匹配度最高；D00027953'修改人员工号'定义'新增或维护相关记录的人员员工号'，语义相近但名称'修改人'与上传维护场景的契合度略低于'更新人'；D00044690'建立人工号'指向参数建立人员，偏创建场景；D00012394'发起人工号'指向流程发起人；D00037294'录入模板人员编号'虽涉及模板录入人员，但标准为'编号'而非'工号'，与字段类型不符；D00017732'配置人员工号'限定数据预警配置；D00027668'操作员工号'、D00028491'用户员工号'过于宽泛；其余备选（文件可见人、文号使用用户、推送任务、经办人、评分人、审核人、测评人、联系人、拓展人、处理人、收款人、维护客户经理等）均为其他特定业务角色，与模板维护无关；D00035928'应用模板页面功能码'、D00035920'流程组件模板编号'、D00028464'流程模板版本号'、D00022094'更新人账号'、D00018438'操作人账号'、D00039639'模板邀请码'等与工号概念不符。权衡：D00027859的名称与业务定义最贴合'维护模板人员工号'的语义，故选择'复用已有标准'。</t>
-  </si>
-  <si>
     <t>D00012394 发起人工号
 D00044690 建立人工号
 D00027859 更新人员工号
@@ -1491,9 +1479,6 @@
     <t>文件上传时间戳</t>
   </si>
   <si>
-    <t>先分析字段：名称'上传时间'，业务含义'通过参数模板管理功能，上传模板时的时间'，核心语义是'模板上传至系统的时间点'。逐一分析备选：D00020828'文件上传时间戳'名称与字段高度相关，业务定义'指文件或数据等信息上传系统的时间节点，包含年月日和时分秒（含毫秒）'，与字段'上传模板时的时间'语义完全吻合，匹配度最高；D00028115'上传文件截止时间戳'定义'截止上传的最后日期时间'，是截止时间而非上传时间，语义相反；D00082379'上报时间戳'为'上报'而非'上传'，场景不同；D00038807'模板生成时间戳'为模板创建生成时间，与上传时间不同；D00035305'模板结束时间戳'、D00035306'模板开始时间戳'为模板使用起止时间；D00031978'配置时间戳'为参数配置时间；D00033373'贝壳影像文件创建时间戳'为特定影像文件创建时间，均与字段语义不符。权衡：D00020828在名称与业务定义两个维度均完全匹配，故选择'复用已有标准'，无需扩展。</t>
-  </si>
-  <si>
     <t>D00028115 上传文件截止时间戳
 D00020828 文件上传时间戳
 D00082379 上报时间戳
@@ -1505,9 +1490,6 @@
   </si>
   <si>
     <t>通过参数模板管理功能，维护模板后该模板的状态</t>
-  </si>
-  <si>
-    <t>先分析字段：名称'状态'，业务含义'通过参数模板管理功能，维护模板后该模板的状态'，核心语义是'模板维护后的状态'。逐一分析备选：D00089729'状态标志'名称与字段相近，但业务定义'事件状态的标志，0-正常;1-废弃'限定为事件状态，与模板状态语义不符；D00034560'维护状态标志'定义'客户或商户是否维护状态的标志'，虽含'维护'字样但对象为客户/商户；D00021081'默认模板标志'、D00021079'临时模板标志'、D00015489'短信模板标志'、D00072124'模板标志'均为关于模板属性的标志（是否为默认、临时、短信模板等），不是模板的状态；D00017604'账户手工状态标志'、D00014678'手工状态变更标志'、D00015603'自动状态变更标志'、D00016010'卡状态变更标志'、D00015212'打印状态标志'、D00021646'资金账号状态标志'、D00082704'询证使用状态标志'、D00015110'止付状态标志'、D00038166'呆滞状态标志'、D00088954'签约状态标志'、D00027048'配置完成标志'、D00037337'测试通过标志'、D00080437'管理信息阶段发送标志'、D00034597'参数显示标志'、D00014787'允许被维护标志'、D00033740'需要维护核心属性标志'等均为各自业务领域的特定状态标志，与模板状态均不匹配。权衡：所有备选均为特定领域的状态/标志概念，没有任何一个可准确覆盖'模板维护后的状态'，通过扩展已有定义也无法自然涵盖，故判定'新增标准'。</t>
   </si>
   <si>
     <t>D00034560 维护状态标志
@@ -1552,9 +1534,6 @@
     <t>用户角色编号</t>
   </si>
   <si>
-    <t>先分析字段：名称'角色编号'，业务含义'角色数据权限维护功能维护的EUIF角色编号'，核心语义是'EUIF系统中角色的编号'。逐一分析备选：D00038697'用户角色编号'名称与字段高度相关，业务定义'系统中按照相关规则，设定的用户角色的编号，用于区分每个角色'，与字段'角色编号'语义完全吻合，匹配度最高；D00090287'角色代码'定义'用于识别用户角色的代码'，名称虽相关但字段为'编号'，'代码'与'编号'概念存在差异；D00085863'角色主键'定义为自增主键、系统生成唯一值，是主键而非业务编号；D00028926'节点接收角色编号'限定流程节点接收任务场景；D00016085'层次角色编号'、D00016383'客户角色编号'为特定对象角色；D00047070'创建人角色编号'、D00002465'冻结人角色编号'为特定操作角色；D00037883'权限编号'、D00089019'主任务编号'、D00090632'所属核心系统编号'、D00016339'合约角色地址编码'、D00031638'邮索行SWIFT码'等均与字段语义不符。权衡：D00038697在名称与业务定义两个维度均最匹配，故选择'复用已有标准'，无需扩展。</t>
-  </si>
-  <si>
     <t>D00038697 用户角色编号
 D00016085 层次角色编号
 D00047070 创建人角色编号
@@ -1618,9 +1597,6 @@
   </si>
   <si>
     <t>角色数据权限维护功能维护的数据权限类型代码</t>
-  </si>
-  <si>
-    <t>先分析字段：名称'数据权限类型代码'，业务含义'角色数据权限维护功能维护的数据权限类型代码'，核心语义是'数据权限类型的代码'。逐一分析备选：D00037883'权限编号'定义'用户具有的权限编号'，是具体权限的编号，而非数据权限类型的代码；D00090287'角色代码'定义'识别用户角色的代码'，是角色代码而非权限类型代码；D00036947'数据字典代码编号'、D00029443'字典类型编号'为数据字典相关编号；D00014513'授权算法号码'、D00067115'支付授权编号'、D00014429'授权验证码'、D00021676'授权应答码'、D00030989'调整授权凭证类型编码'、D00035425'被授权账号'、D00000029'授权柜员编号'、D00003096'发票作废授权柜员编号'均为授权场景相关；D00090001'数据来源编码'为数据来源编码；D00044811'账单数据记录类型编码'、D00082404'政府金融冻结账号类型代码'、D00044778'风险类型规则代码编号'为特定领域类型编码；D00089715'券商权限编号'为券商特定权限；D00033517'用户账户权限表主键'、D00019344'部门类型主键'为主键；D00028926'节点接收角色编号'、D00090632'所属核心系统编号'、D00048456'任务分派目标编号'等均与'数据权限类型代码'语义不符。权衡：所有备选均未覆盖'数据权限类型代码'这一概念，既有标准中无'数据权限类型'相关定义，通过扩展也无法自然覆盖，故判定'新增标准'。</t>
   </si>
   <si>
     <t>D00037883 权限编号
@@ -1694,9 +1670,6 @@
   </si>
   <si>
     <t>编码值</t>
-  </si>
-  <si>
-    <t>先分析字段：名称'数据权限代码KEY值1'，业务含义'角色数据权限维护功能维护的数据权限代码KEY值1（共5个属性）'，数据示例'DHSPLX'。核心语义是：在角色数据权限配置中，以键值对方式表示数据权限属性时，键（KEY）所对应的代码取值，本质是一个代码值。逐一分析备选：D00033517'用户账户权限表主键'是权限表记录的系统主键，用于标识表内记录，与代码取值语义不同，排除；D00036934'Key编号'中Key指序列号生成器（硬件），与数据权限代码KEY值无关，排除；D00037588'KEY序列号'指二代Key硬件生成的序列号，同属硬件概念，排除；D00037883'权限编号'指用户具有的权限实例编号，本字段是权限配置中的代码值而非权限实例编号，排除；D00090287'角色代码'是识别用户角色的代码，本字段虽在角色数据权限功能下维护，但字段本身是权限代码KEY值而非角色代码，排除；D00019162'职位主键'、D00019428'职位簇主键'、D00019004'父类职务主键'均为人资职位体系唯一编号，与数据权限无关，排除；D00028081'关注授权模板编号'为关注功能模块编号，无关，排除；D00037807'编码值'指字段编码的代码取值，本字段名称含'代码'与'值'，业务含义即数据权限属性的代码取值，名称与定义高度匹配，为最优候选；D00036947'数据字典代码编号'偏重代码取值的编号而非代码取值本身，匹配度次之；D00089715'券商权限编号'范围过窄且限定券商场景，排除；D00010563'数据版本编号'、D00014645'报表数据编号'、D00028926'节点接收角色编号'、D00090632'所属核心系统编号'、D00048456'任务分派目标编号'分别为数据版本、报表、流程角色、核心系统、任务分派场景的编号，均与本字段代码值语义不符，排除；D00000029'授权柜员编号'、D00035425'被授权账号'、D00003096'发票作废授权柜员编号'、D00033884'授权用户号'均为授权主体/账号类字段，与代码值语义不符，排除。权衡：编码值在名称与业务定义两个维度均与字段高度吻合，数据示例'DHSPLX'即一个代码取值，可直接复用且定义无需扩展，故选择'复用已有标准'。</t>
   </si>
   <si>
     <t>D00033517 用户账户权限表主键
@@ -2308,34 +2281,6 @@
     <t>01-停用;02-启用</t>
   </si>
   <si>
-    <t>关联参数模板维护功能，维护人员通过功能输入的模板状态</t>
-  </si>
-  <si>
-    <t>先分析字段：名称'模板状态'，业务含义'维护人员通过功能输入的模板状态'，核心语义是'模板本身所处的状态'，数据示例01为状态编码。逐一分析备选：D00072124'模板标志'名称虽含'模板'，但业务定义'用于标识判断目标数据是否为模板'是判断数据是否为模板的标识，与模板自身状态是不同概念；D00021081'默认模板标志'、D00021079'临时模板标志'、D00015489'短信模板标志'分别为默认/临时/短信类型判断标志，均非模板状态；D00034560'维护状态标志'定义'客户或商户是否维护状态的标志'，对象为客户/商户且语义是维护与否，与模板状态无关；D00089729'状态标志'为通用状态标志但定义限定'事件状态的标志'，对象为事件，与模板主体不符；D00042176'维护标志'、D00014787'允许被维护标志'、D00031361'维护人标志'等为维护相关标志，与模板状态概念不同；其余D00017604、D00014172、D00019385、D00067034、D00023103、D00015110、D00015212、D00038166、D00088954、D00047653、D00037337等均为各类特定业务标志。权衡：所有备选均为'标志'类概念且业务定义集中于'是否为某类对象/状态'的判断，与'模板自身所处的状态（如有效、停用等）'语义均不匹配，且各标志定义与模板状态属于不同业务对象与含义，无法通过扩展某一通用标志的定义来准确覆盖'模板状态'，故判定'新增标准'。</t>
-  </si>
-  <si>
-    <t>D00072124 模板标志
-D00021081 默认模板标志
-D00021079 临时模板标志
-D00015489 短信模板标志
-D00034560 维护状态标志
-D00017604 账户手工状态标志
-D00014172 系统开放模式标志
-D00019385 跨行调动状态标志
-D00067034 参与代发或时序模型评分标志
-D00023103 对公手机银行配置服务授权模式标志
-D00089729 状态标志
-D00015110 止付状态标志
-D00015212 打印状态标志
-D00038166 呆滞状态标志
-D00088954 签约状态标志
-D00031361 维护人标志
-D00047653 关联菜单功能标志
-D00014787 允许被维护标志
-D00042176 维护标志
-D00037337 测试通过标志</t>
-  </si>
-  <si>
     <t>模板类型</t>
   </si>
   <si>
@@ -2386,9 +2331,6 @@
   </si>
   <si>
     <t>团队编号</t>
-  </si>
-  <si>
-    <t>先分析字段：名称'参数模板归属团队'，业务含义'关联参数模板维护功能，维护人员通过功能选择的参数模板归属团队'，数据示例'TD0015'，核心语义是'参数模板所属团队的编号/标识'。逐一分析备选：D00045559团队编号，业务定义'指相关工作团队的编号'，名称与语义均为通用团队标识，与本字段'归属团队'完全匹配，匹配度最高；D00089551团队代码，业务定义限定'销售团队'，适用范围窄于本字段；D00038571虚拟团队编号，指绩效考核定义的虚拟团队，概念不同；其余备选如D00028446参数编号、D00017911模板编号、D00035920流程组件模板编号、D00037294录入模板人员编号、D00044690建立人工号、D00022094更新人账号等，均是参数/模板/人员编号，而非团队概念，均不匹配。权衡：D00045559团队编号名称与业务定义均为通用团队标识，可直接覆盖参数模板归属团队的场景，无需扩展，故选择'复用已有标准'。</t>
   </si>
   <si>
     <t>D00035920 流程组件模板编号
@@ -3451,6 +3393,77 @@
   </si>
   <si>
     <t>系统自动生成的客户唯一编号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先分析字段：名称'参数模板名称'，业务含义'通过参数模板管理功能，由维护人员填写的参数模板名称'，核心语义是参数模板的名称，属于'模板名称'大类下的参数模板细分。逐一分析备选：D00017912'模板名称'业务定义'短信、邮件等预定义固定格式模板的名称'，是通用模板名称概念，字段'参数模板'正是一种模板，语义同源但原定义仅列举短信、邮件模板，未明确覆盖参数模板；D00028451'参数名称'是参数本身的名称为便于参数管理设定，不包含'模板'概念；D00036116'应用模板名称'限定应用组件模板、D00028466'流程模板名称'限定流程模板，均为其他模板类型；D00034631'短信模板参数'、D00034086'JOB参数名'、D00085852'功能输入参数'等与模板名称概念不同。权衡：字段与D00017912'模板名称'语义同源，直接判定新增会丢弃已有标准，判定直接复用则原定义未显式覆盖参数模板；通过扩展定义将参数模板纳入'模板名称'覆盖范围，既复用标准又满足字段需要，故选择'复用已有标准但扩展业务定义'。 扩展建议: 短信、邮件、参数等预定义固定格式模板的名称，包括通过参数模板管理功能由维护人员填写的参数模板名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先分析字段：名称'参数表编号'，业务含义'通过参数模板管理功能，由维护人员填写的参数表编号'，数据示例'CS0001'，核心语义是参数体系中的编号，用于参数管理。逐一分析备选：D00028446'参数编号'业务定义'参数在使用过程中，为了便于参数管理，而设定的编号'，与字段'参数表编号'同属参数管理编号体系，语义最匹配，匹配度最高；D00029464'参考数据编号'、D00029580'上级参考数据编号'针对参考数据机制，与参数编号有差异；D00018195'客户参数编号'限定客户参考信息、D00034642'审核配置参数编号'限定审核配置、D00016051'SWIFT参数编号'、D00016815'联行号参数编号'、D00088531'余额核算参数编号'、D00017138'信息项统计参数编号'均为特定业务参数编号，范围窄于字段的通用参数表编号；D00001473'核算参数码'、D00001474'计息参数码'、D00050497'核查功能码'为参数码概念；其余为表单编号、报表编号、员工号等，与参数编号无关。权衡：D00028446'参数编号'的定义'为了便于参数管理而设定的编号'与字段的'参数表编号'语义一致，覆盖面合适，故选择复用D00028446，无需扩展。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先分析字段：名称'文件编号（doc_id）'，业务含义'通过参数模板管理功能，上传模板到ECM后返回的doc_id字段'，数据示例'20260604603_30000277_01001'，核心语义是ECM系统中对上传文件生成的编号。逐一分析备选：D00027232'ECM文件编号'业务定义'ECM系统中对每个文件生成的编号，主要用来区分不同的文件'，与字段'上传模板到ECM后返回的doc_id'在系统场景与语义上完全对应，匹配度最高；D00012320'文件编号'是通用文件编号，虽名称与字段更接近但未体现ECM场景，精确度低于D00027232；D00021829'数据文件编号'限定传输数据文件、D00027874'文件组编号'限定文件组、D00027353'文件主编号'是上级编号、D00028906'文件夹编号'是目录编号、D00028454'错误文件编号'限定错误文件、D00047613'介绍信文件编号'、D00027887'GUOP文件编号'、D00028369'稿纸文件编号'、D00018422'银银平台文件编号'均为其他特定系统或场景的文件编号，与ECM场景不符。权衡：字段明确为ECM上传后返回的doc_id，D00027232的业务定义最精确地覆盖该场景，按'选择业务定义最精确、覆盖面最合适'的原则，选择复用D00027232，无需扩展。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先分析字段：名称'上传人工号'，业务含义'通过参数模板管理功能，维护模板，维护人员的工号'，核心语义是'维护模板人员的工号'。逐一分析备选：D00027859'更新人员工号'业务定义'表示维护相关记录的人员员工号信息'，与字段中'维护模板、维护人员'的语义高度吻合，匹配度最高；D00027953'修改人员工号'定义'新增或维护相关记录的人员员工号'，语义相近但名称'修改人'与上传维护场景的契合度略低于'更新人'；D00044690'建立人工号'指向参数建立人员，偏创建场景；D00012394'发起人工号'指向流程发起人；D00037294'录入模板人员编号'虽涉及模板录入人员，但标准为'编号'而非'工号'，与字段类型不符；D00017732'配置人员工号'限定数据预警配置；D00027668'操作员工号'、D00028491'用户员工号'过于宽泛；其余备选（文件可见人、文号使用用户、推送任务、经办人、评分人、审核人、测评人、联系人、拓展人、处理人、收款人、维护客户经理等）均为其他特定业务角色，与模板维护无关；D00035928'应用模板页面功能码'、D00035920'流程组件模板编号'、D00028464'流程模板版本号'、D00022094'更新人账号'、D00018438'操作人账号'、D00039639'模板邀请码'等与工号概念不符。权衡：D00027859的名称与业务定义最贴合'维护模板人员工号'的语义，故选择'复用已有标准'。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先分析字段：名称'上传时间'，业务含义'通过参数模板管理功能，上传模板时的时间'，核心语义是'模板上传至系统的时间点'。逐一分析备选：D00020828'文件上传时间戳'名称与字段高度相关，业务定义'指文件或数据等信息上传系统的时间节点，包含年月日和时分秒（含毫秒）'，与字段'上传模板时的时间'语义完全吻合，匹配度最高；D00028115'上传文件截止时间戳'定义'截止上传的最后日期时间'，是截止时间而非上传时间，语义相反；D00082379'上报时间戳'为'上报'而非'上传'，场景不同；D00038807'模板生成时间戳'为模板创建生成时间，与上传时间不同；D00035305'模板结束时间戳'、D00035306'模板开始时间戳'为模板使用起止时间；D00031978'配置时间戳'为参数配置时间；D00033373'贝壳影像文件创建时间戳'为特定影像文件创建时间，均与字段语义不符。权衡：D00020828在名称与业务定义两个维度均完全匹配，故选择'复用已有标准'，无需扩展。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先分析字段：名称'状态'，业务含义'通过参数模板管理功能，维护模板后该模板的状态'，核心语义是'模板维护后的状态'。逐一分析备选：D00089729'状态标志'名称与字段相近，但业务定义'事件状态的标志，0-正常;1-废弃'限定为事件状态，与模板状态语义不符；D00034560'维护状态标志'定义'客户或商户是否维护状态的标志'，虽含'维护'字样但对象为客户/商户；D00021081'默认模板标志'、D00021079'临时模板标志'、D00015489'短信模板标志'、D00072124'模板标志'均为关于模板属性的标志（是否为默认、临时、短信模板等），不是模板的状态；D00017604'账户手工状态标志'、D00014678'手工状态变更标志'、D00015603'自动状态变更标志'、D00016010'卡状态变更标志'、D00015212'打印状态标志'、D00021646'资金账号状态标志'、D00082704'询证使用状态标志'、D00015110'止付状态标志'、D00038166'呆滞状态标志'、D00088954'签约状态标志'、D00027048'配置完成标志'、D00037337'测试通过标志'、D00080437'管理信息阶段发送标志'、D00034597'参数显示标志'、D00014787'允许被维护标志'、D00033740'需要维护核心属性标志'等均为各自业务领域的特定状态标志，与模板状态均不匹配。权衡：所有备选均为特定领域的状态/标志概念，没有任何一个可准确覆盖'模板维护后的状态'，通过扩展已有定义也无法自然涵盖，故判定'新增标准'。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先分析字段：名称'角色编号'，业务含义'角色数据权限维护功能维护的EUIF角色编号'，核心语义是'EUIF系统中角色的编号'。逐一分析备选：D00038697'用户角色编号'名称与字段高度相关，业务定义'系统中按照相关规则，设定的用户角色的编号，用于区分每个角色'，与字段'角色编号'语义完全吻合，匹配度最高；D00090287'角色代码'定义'用于识别用户角色的代码'，名称虽相关但字段为'编号'，'代码'与'编号'概念存在差异；D00085863'角色主键'定义为自增主键、系统生成唯一值，是主键而非业务编号；D00028926'节点接收角色编号'限定流程节点接收任务场景；D00016085'层次角色编号'、D00016383'客户角色编号'为特定对象角色；D00047070'创建人角色编号'、D00002465'冻结人角色编号'为特定操作角色；D00037883'权限编号'、D00089019'主任务编号'、D00090632'所属核心系统编号'、D00016339'合约角色地址编码'、D00031638'邮索行SWIFT码'等均与字段语义不符。权衡：D00038697在名称与业务定义两个维度均最匹配，故选择'复用已有标准'，无需扩展。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先分析字段：名称'数据权限类型代码'，业务含义'角色数据权限维护功能维护的数据权限类型代码'，核心语义是'数据权限类型的代码'。逐一分析备选：D00037883'权限编号'定义'用户具有的权限编号'，是具体权限的编号，而非数据权限类型的代码；D00090287'角色代码'定义'识别用户角色的代码'，是角色代码而非权限类型代码；D00036947'数据字典代码编号'、D00029443'字典类型编号'为数据字典相关编号；D00014513'授权算法号码'、D00067115'支付授权编号'、D00014429'授权验证码'、D00021676'授权应答码'、D00030989'调整授权凭证类型编码'、D00035425'被授权账号'、D00000029'授权柜员编号'、D00003096'发票作废授权柜员编号'均为授权场景相关；D00090001'数据来源编码'为数据来源编码；D00044811'账单数据记录类型编码'、D00082404'政府金融冻结账号类型代码'、D00044778'风险类型规则代码编号'为特定领域类型编码；D00089715'券商权限编号'为券商特定权限；D00033517'用户账户权限表主键'、D00019344'部门类型主键'为主键；D00028926'节点接收角色编号'、D00090632'所属核心系统编号'、D00048456'任务分派目标编号'等均与'数据权限类型代码'语义不符。权衡：所有备选均未覆盖'数据权限类型代码'这一概念，既有标准中无'数据权限类型'相关定义，通过扩展也无法自然覆盖，故判定'新增标准'。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先分析字段：名称'数据权限代码KEY值1'，业务含义'角色数据权限维护功能维护的数据权限代码KEY值1（共5个属性）'，数据示例'DHSPLX'。核心语义是：在角色数据权限配置中，以键值对方式表示数据权限属性时，键（KEY）所对应的代码取值，本质是一个代码值。逐一分析备选：D00033517'用户账户权限表主键'是权限表记录的系统主键，用于标识表内记录，与代码取值语义不同，排除；D00036934'Key编号'中Key指序列号生成器（硬件），与数据权限代码KEY值无关，排除；D00037588'KEY序列号'指二代Key硬件生成的序列号，同属硬件概念，排除；D00037883'权限编号'指用户具有的权限实例编号，本字段是权限配置中的代码值而非权限实例编号，排除；D00090287'角色代码'是识别用户角色的代码，本字段虽在角色数据权限功能下维护，但字段本身是权限代码KEY值而非角色代码，排除；D00019162'职位主键'、D00019428'职位簇主键'、D00019004'父类职务主键'均为人资职位体系唯一编号，与数据权限无关，排除；D00028081'关注授权模板编号'为关注功能模块编号，无关，排除；D00037807'编码值'指字段编码的代码取值，本字段名称含'代码'与'值'，业务含义即数据权限属性的代码取值，名称与定义高度匹配，为最优候选；D00036947'数据字典代码编号'偏重代码取值的编号而非代码取值本身，匹配度次之；D00089715'券商权限编号'范围过窄且限定券商场景，排除；D00010563'数据版本编号'、D00014645'报表数据编号'、D00028926'节点接收角色编号'、D00090632'所属核心系统编号'、D00048456'任务分派目标编号'分别为数据版本、报表、流程角色、核心系统、任务分派场景的编号，均与本字段代码值语义不符，排除；D00000029'授权柜员编号'、D00035425'被授权账号'、D00003096'发票作废授权柜员编号'、D00033884'授权用户号'均为授权主体/账号类字段，与代码值语义不符，排除。权衡：编码值在名称与业务定义两个维度均与字段高度吻合，数据示例'DHSPLX'即一个代码取值，可直接复用且定义无需扩展，故选择'复用已有标准'。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先分析字段：名称'模板状态'，业务含义'维护人员通过功能输入的模板状态'，核心语义是'模板本身所处的状态'，数据示例01为状态编码。逐一分析备选：D00072124'模板标志'名称虽含'模板'，但业务定义'用于标识判断目标数据是否为模板'是判断数据是否为模板的标识，与模板自身状态是不同概念；D00021081'默认模板标志'、D00021079'临时模板标志'、D00015489'短信模板标志'分别为默认/临时/短信类型判断标志，均非模板状态；D00034560'维护状态标志'定义'客户或商户是否维护状态的标志'，对象为客户/商户且语义是维护与否，与模板状态无关；D00089729'状态标志'为通用状态标志但定义限定'事件状态的标志'，对象为事件，与模板主体不符；D00042176'维护标志'、D00014787'允许被维护标志'、D00031361'维护人标志'等为维护相关标志，与模板状态概念不同；其余D00017604、D00014172、D00019385、D00067034、D00023103、D00015110、D00015212、D00038166、D00088954、D00047653、D00037337等均为各类特定业务标志。权衡：所有备选均为'标志'类概念且业务定义集中于'是否为某类对象/状态'的判断，与'模板自身所处的状态（如有效、停用等）'语义均不匹配，且各标志定义与模板状态属于不同业务对象与含义，无法通过扩展某一通用标志的定义来准确覆盖'模板状态'，故判定'新增标准'。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D00072124 模板标志
+D00021081 默认模板标志
+D00021079 临时模板标志
+D00015489 短信模板标志
+D00034560 维护状态标志
+D00017604 账户手工状态标志
+D00014172 系统开放模式标志
+D00019385 跨行调动状态标志
+D00067034 参与代发或时序模型评分标志
+D00023103 对公手机银行配置服务授权模式标志
+D00089729 状态标志
+D00015110 止付状态标志
+D00015212 打印状态标志
+D00038166 呆滞状态标志
+D00088954 签约状态标志
+D00031361 维护人标志
+D00047653 关联菜单功能标志
+D00014787 允许被维护标志
+D00042176 维护标志
+D00037337 测试通过标志</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关联参数模板维护功能，维护人员通过功能输入的模板状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先分析字段：名称'参数模板归属团队'，业务含义'关联参数模板维护功能，维护人员通过功能选择的参数模板归属团队'，数据示例'TD0015'，核心语义是'参数模板所属团队的编号/标识'。逐一分析备选：D00045559团队编号，业务定义'指相关工作团队的编号'，名称与语义均为通用团队标识，与本字段'归属团队'完全匹配，匹配度最高；D00089551团队代码，业务定义限定'销售团队'，适用范围窄于本字段；D00038571虚拟团队编号，指绩效考核定义的虚拟团队，概念不同；其余备选如D00028446参数编号、D00017911模板编号、D00035920流程组件模板编号、D00037294录入模板人员编号、D00044690建立人工号、D00022094更新人账号等，均是参数/模板/人员编号，而非团队概念，均不匹配。权衡：D00045559团队编号名称与业务定义均为通用团队标识，可直接覆盖参数模板归属团队的场景，无需扩展，故选择'复用已有标准'。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3547,7 +3560,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3594,6 +3607,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3601,11 +3620,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3926,13 +3942,14 @@
     <col min="12" max="12" width="4.44140625" customWidth="1"/>
     <col min="13" max="13" width="6.109375" customWidth="1"/>
     <col min="14" max="14" width="5.109375" customWidth="1"/>
-    <col min="15" max="15" width="14.88671875" customWidth="1"/>
+    <col min="15" max="15" width="19.77734375" customWidth="1"/>
     <col min="17" max="17" width="24" style="1" customWidth="1"/>
     <col min="18" max="18" width="11.77734375" customWidth="1"/>
     <col min="19" max="19" width="13" hidden="1" customWidth="1"/>
     <col min="20" max="20" width="5.33203125" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="20.109375" customWidth="1"/>
+    <col min="23" max="23" width="15.33203125" customWidth="1"/>
+    <col min="24" max="24" width="0" hidden="1" customWidth="1"/>
     <col min="25" max="25" width="36.33203125" customWidth="1"/>
     <col min="26" max="26" width="16.44140625" customWidth="1"/>
     <col min="27" max="27" width="19" customWidth="1"/>
@@ -3942,43 +3959,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="18" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="19"/>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19"/>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19"/>
-      <c r="W1" s="19"/>
-      <c r="X1" s="19"/>
-      <c r="Y1" s="19"/>
-      <c r="Z1" s="19"/>
-      <c r="AA1" s="19" t="s">
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="21"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="21"/>
+      <c r="S1" s="21"/>
+      <c r="T1" s="21"/>
+      <c r="U1" s="21"/>
+      <c r="V1" s="21"/>
+      <c r="W1" s="21"/>
+      <c r="X1" s="21"/>
+      <c r="Y1" s="21"/>
+      <c r="Z1" s="21"/>
+      <c r="AA1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="AB1" s="19"/>
-      <c r="AC1" s="19"/>
-      <c r="AD1" s="19"/>
-      <c r="AE1" s="19"/>
+      <c r="AB1" s="21"/>
+      <c r="AC1" s="21"/>
+      <c r="AD1" s="21"/>
+      <c r="AE1" s="21"/>
     </row>
     <row r="2" spans="1:31">
       <c r="A2" t="s">
@@ -4516,7 +4533,7 @@
         <v>107</v>
       </c>
       <c r="AD14" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="AE14" s="7" t="s">
         <v>108</v>
@@ -4554,7 +4571,7 @@
         <v>113</v>
       </c>
       <c r="AD15" t="s">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="AE15" s="7" t="s">
         <v>114</v>
@@ -4814,10 +4831,10 @@
         <v>152</v>
       </c>
       <c r="AD22" t="s">
-        <v>581</v>
+        <v>568</v>
       </c>
       <c r="AE22" s="4" t="s">
-        <v>580</v>
+        <v>567</v>
       </c>
     </row>
     <row r="23" spans="10:31">
@@ -4966,7 +4983,7 @@
         <v>178</v>
       </c>
       <c r="AD26" t="s">
-        <v>582</v>
+        <v>569</v>
       </c>
       <c r="AE26" s="7" t="s">
         <v>179</v>
@@ -4982,7 +4999,7 @@
       <c r="P27" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="Q27" s="21">
+      <c r="Q27" s="18">
         <v>45292</v>
       </c>
       <c r="R27" s="15" t="s">
@@ -5142,7 +5159,7 @@
         <v>38</v>
       </c>
       <c r="Y31" s="15" t="s">
-        <v>584</v>
+        <v>571</v>
       </c>
       <c r="AA31" s="15" t="s">
         <v>39</v>
@@ -5154,7 +5171,7 @@
         <v>204</v>
       </c>
       <c r="AD31" s="15" t="s">
-        <v>583</v>
+        <v>570</v>
       </c>
       <c r="AE31" s="17" t="s">
         <v>205</v>
@@ -5199,28 +5216,28 @@
       </c>
     </row>
     <row r="33" spans="10:31" s="15" customFormat="1" ht="30" customHeight="1">
-      <c r="J33" s="22" t="s">
+      <c r="J33" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="O33" s="22" t="s">
+      <c r="O33" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="P33" s="22" t="s">
+      <c r="P33" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="Q33" s="22" t="s">
+      <c r="Q33" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="R33" s="22" t="s">
+      <c r="R33" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="V33" s="22" t="s">
+      <c r="V33" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="W33" s="22" t="s">
+      <c r="W33" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="Y33" s="22" t="s">
+      <c r="Y33" s="19" t="s">
         <v>217</v>
       </c>
     </row>
@@ -5257,10 +5274,10 @@
         <v>224</v>
       </c>
       <c r="AD34" t="s">
+        <v>572</v>
+      </c>
+      <c r="AE34" s="7" t="s">
         <v>225</v>
-      </c>
-      <c r="AE34" s="7" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="35" spans="10:31" ht="30" customHeight="1">
@@ -5268,13 +5285,13 @@
         <v>218</v>
       </c>
       <c r="O35" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="P35" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="P35" s="5" t="s">
+      <c r="Q35" s="5" t="s">
         <v>228</v>
-      </c>
-      <c r="Q35" s="5" t="s">
-        <v>229</v>
       </c>
       <c r="R35" s="5" t="s">
         <v>105</v>
@@ -5284,22 +5301,22 @@
       </c>
       <c r="W35" s="5"/>
       <c r="Y35" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AA35" t="s">
         <v>39</v>
       </c>
       <c r="AB35" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC35" t="s">
         <v>231</v>
       </c>
-      <c r="AC35" t="s">
+      <c r="AD35" t="s">
+        <v>573</v>
+      </c>
+      <c r="AE35" s="7" t="s">
         <v>232</v>
-      </c>
-      <c r="AD35" t="s">
-        <v>233</v>
-      </c>
-      <c r="AE35" s="7" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="36" spans="10:31" ht="30" customHeight="1">
@@ -5307,13 +5324,13 @@
         <v>218</v>
       </c>
       <c r="O36" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="P36" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q36" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="R36" s="5" t="s">
         <v>105</v>
@@ -5323,22 +5340,22 @@
       </c>
       <c r="W36" s="5"/>
       <c r="Y36" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="AA36" t="s">
         <v>39</v>
       </c>
       <c r="AB36" t="s">
+        <v>236</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>237</v>
+      </c>
+      <c r="AD36" t="s">
+        <v>574</v>
+      </c>
+      <c r="AE36" s="7" t="s">
         <v>238</v>
-      </c>
-      <c r="AC36" t="s">
-        <v>239</v>
-      </c>
-      <c r="AD36" t="s">
-        <v>240</v>
-      </c>
-      <c r="AE36" s="7" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="37" spans="10:31" ht="30" customHeight="1">
@@ -5346,13 +5363,13 @@
         <v>218</v>
       </c>
       <c r="O37" s="5" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="P37" s="5" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="Q37" s="5" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="R37" s="5" t="s">
         <v>169</v>
@@ -5362,22 +5379,22 @@
       </c>
       <c r="W37" s="5"/>
       <c r="Y37" s="5" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AA37" t="s">
         <v>39</v>
       </c>
       <c r="AB37" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>244</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>245</v>
+      </c>
+      <c r="AE37" s="7" t="s">
         <v>246</v>
-      </c>
-      <c r="AC37" t="s">
-        <v>247</v>
-      </c>
-      <c r="AD37" t="s">
-        <v>248</v>
-      </c>
-      <c r="AE37" s="7" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="38" spans="10:31" ht="30" customHeight="1">
@@ -5385,13 +5402,13 @@
         <v>218</v>
       </c>
       <c r="O38" s="5" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P38" s="5" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="Q38" s="5" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="R38" s="5" t="s">
         <v>105</v>
@@ -5401,22 +5418,22 @@
       </c>
       <c r="W38" s="5"/>
       <c r="Y38" s="5" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AA38" t="s">
         <v>39</v>
       </c>
       <c r="AB38" t="s">
+        <v>251</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>252</v>
+      </c>
+      <c r="AD38" t="s">
+        <v>253</v>
+      </c>
+      <c r="AE38" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="AC38" t="s">
-        <v>255</v>
-      </c>
-      <c r="AD38" t="s">
-        <v>256</v>
-      </c>
-      <c r="AE38" s="7" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="39" spans="10:31" ht="30" customHeight="1">
@@ -5424,13 +5441,13 @@
         <v>218</v>
       </c>
       <c r="O39" s="5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P39" s="5" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="Q39" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="R39" s="5" t="s">
         <v>105</v>
@@ -5440,22 +5457,22 @@
       </c>
       <c r="W39" s="5"/>
       <c r="Y39" s="5" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AA39" t="s">
         <v>39</v>
       </c>
       <c r="AB39" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AC39" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AD39" t="s">
-        <v>264</v>
+        <v>575</v>
       </c>
       <c r="AE39" s="7" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="40" spans="10:31" ht="30" customHeight="1">
@@ -5463,13 +5480,13 @@
         <v>218</v>
       </c>
       <c r="O40" s="5" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="P40" s="5" t="s">
         <v>167</v>
       </c>
       <c r="Q40" s="5" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="R40" s="5" t="s">
         <v>169</v>
@@ -5479,22 +5496,22 @@
       </c>
       <c r="W40" s="5"/>
       <c r="Y40" s="5" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="AA40" t="s">
         <v>39</v>
       </c>
       <c r="AB40" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AC40" t="s">
+        <v>262</v>
+      </c>
+      <c r="AD40" t="s">
         <v>266</v>
       </c>
-      <c r="AD40" t="s">
-        <v>270</v>
-      </c>
       <c r="AE40" s="7" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="41" spans="10:31" ht="30" customHeight="1">
@@ -5502,13 +5519,13 @@
         <v>218</v>
       </c>
       <c r="O41" s="5" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="P41" s="5" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="Q41" s="5" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="R41" s="5" t="s">
         <v>47</v>
@@ -5518,22 +5535,22 @@
       </c>
       <c r="W41" s="5"/>
       <c r="Y41" s="5" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="AA41" t="s">
         <v>39</v>
       </c>
       <c r="AB41" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AC41" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="AD41" t="s">
-        <v>278</v>
+        <v>576</v>
       </c>
       <c r="AE41" s="7" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="42" spans="10:31" ht="30" customHeight="1">
@@ -5559,69 +5576,69 @@
         <v>216</v>
       </c>
       <c r="Y42" s="5" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="AA42" t="s">
         <v>128</v>
       </c>
       <c r="AD42" t="s">
+        <v>577</v>
+      </c>
+      <c r="AE42" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="43" spans="10:31" s="15" customFormat="1" ht="30" customHeight="1">
+      <c r="J43" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="O43" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="P43" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q43" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="R43" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="V43" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="W43" s="19"/>
+      <c r="Y43" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="AA43" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB43" s="15" t="s">
         <v>281</v>
       </c>
-      <c r="AE42" s="7" t="s">
+      <c r="AC43" s="15" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="43" spans="10:31" ht="30" customHeight="1">
-      <c r="J43" s="5" t="s">
+      <c r="AD43" s="15" t="s">
+        <v>578</v>
+      </c>
+      <c r="AE43" s="17" t="s">
         <v>283</v>
-      </c>
-      <c r="O43" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="P43" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q43" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="R43" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="V43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="W43" s="5"/>
-      <c r="Y43" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="AA43" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB43" t="s">
-        <v>287</v>
-      </c>
-      <c r="AC43" t="s">
-        <v>288</v>
-      </c>
-      <c r="AD43" t="s">
-        <v>289</v>
-      </c>
-      <c r="AE43" s="7" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="44" spans="10:31" ht="30" customHeight="1">
       <c r="J44" s="5" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="O44" s="5" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="P44" s="5" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="Q44" s="5" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="R44" s="5" t="s">
         <v>169</v>
@@ -5631,36 +5648,36 @@
       </c>
       <c r="W44" s="5"/>
       <c r="Y44" s="5" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="AA44" t="s">
         <v>39</v>
       </c>
       <c r="AB44" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="AC44" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="AD44" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="AE44" s="7" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
     </row>
     <row r="45" spans="10:31" ht="30" customHeight="1">
       <c r="J45" s="5" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="O45" s="5" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="P45" s="5" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="Q45" s="5" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="R45" s="5" t="s">
         <v>105</v>
@@ -5670,30 +5687,30 @@
       </c>
       <c r="W45" s="5"/>
       <c r="Y45" s="5" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="AA45" t="s">
         <v>128</v>
       </c>
       <c r="AD45" t="s">
-        <v>301</v>
+        <v>579</v>
       </c>
       <c r="AE45" s="7" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
     </row>
     <row r="46" spans="10:31" ht="30" customHeight="1">
       <c r="J46" s="5" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="O46" s="5" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="P46" s="5" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="Q46" s="5" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="R46" s="5" t="s">
         <v>169</v>
@@ -5703,30 +5720,30 @@
       </c>
       <c r="W46" s="5"/>
       <c r="Y46" s="5" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="AA46" t="s">
         <v>128</v>
       </c>
       <c r="AD46" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="AE46" s="7" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="47" spans="10:31" s="3" customFormat="1" ht="30" customHeight="1">
       <c r="J47" s="11" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="O47" s="11" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="P47" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q47" s="11" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="R47" s="11" t="s">
         <v>105</v>
@@ -5736,36 +5753,36 @@
       </c>
       <c r="W47" s="11"/>
       <c r="Y47" s="11" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="AA47" t="s">
         <v>39</v>
       </c>
       <c r="AB47" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="AC47" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="AD47" t="s">
-        <v>312</v>
+        <v>580</v>
       </c>
       <c r="AE47" s="7" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
     </row>
     <row r="48" spans="10:31" s="3" customFormat="1" ht="30" customHeight="1">
       <c r="J48" s="11" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="O48" s="11" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="P48" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q48" s="11" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="R48" s="11" t="s">
         <v>105</v>
@@ -5775,36 +5792,36 @@
       </c>
       <c r="W48" s="11"/>
       <c r="Y48" s="11" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="AA48" t="s">
         <v>39</v>
       </c>
       <c r="AB48" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="AC48" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="AD48" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="AE48" s="7" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
     </row>
     <row r="49" spans="10:31" s="3" customFormat="1" ht="30" customHeight="1">
       <c r="J49" s="11" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="O49" s="11" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="P49" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q49" s="11" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="R49" s="11" t="s">
         <v>105</v>
@@ -5814,36 +5831,36 @@
       </c>
       <c r="W49" s="11"/>
       <c r="Y49" s="11" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="AA49" t="s">
         <v>39</v>
       </c>
       <c r="AB49" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="AC49" t="s">
+        <v>303</v>
+      </c>
+      <c r="AD49" t="s">
         <v>311</v>
       </c>
-      <c r="AD49" t="s">
-        <v>320</v>
-      </c>
       <c r="AE49" s="7" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="10:31" s="3" customFormat="1" ht="30" customHeight="1">
       <c r="J50" s="11" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="O50" s="11" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="P50" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q50" s="11" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="R50" s="11" t="s">
         <v>105</v>
@@ -5853,36 +5870,36 @@
       </c>
       <c r="W50" s="11"/>
       <c r="Y50" s="11" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="AA50" t="s">
         <v>39</v>
       </c>
       <c r="AB50" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="AC50" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="AD50" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="AE50" s="7" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="10:31" s="3" customFormat="1" ht="30" customHeight="1">
       <c r="J51" s="11" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="O51" s="11" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="P51" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q51" s="11" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="R51" s="11" t="s">
         <v>105</v>
@@ -5892,36 +5909,36 @@
       </c>
       <c r="W51" s="11"/>
       <c r="Y51" s="11" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="AA51" t="s">
         <v>39</v>
       </c>
       <c r="AB51" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="AC51" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="AD51" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="AE51" s="7" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52" spans="10:31" s="3" customFormat="1" ht="30" customHeight="1">
       <c r="J52" s="11" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="O52" s="11" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="P52" s="11" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="Q52" s="11" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="R52" s="11" t="s">
         <v>105</v>
@@ -5931,36 +5948,36 @@
       </c>
       <c r="W52" s="11"/>
       <c r="Y52" s="11" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="AA52" t="s">
         <v>39</v>
       </c>
       <c r="AB52" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="AC52" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="AD52" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="AE52" s="7" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
     </row>
     <row r="53" spans="10:31" s="3" customFormat="1" ht="30" customHeight="1">
       <c r="J53" s="11" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="O53" s="11" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="P53" s="11" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="Q53" s="11" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="R53" s="11" t="s">
         <v>105</v>
@@ -5970,36 +5987,36 @@
       </c>
       <c r="W53" s="11"/>
       <c r="Y53" s="11" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="AA53" t="s">
         <v>39</v>
       </c>
       <c r="AB53" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="AC53" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="AD53" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="AE53" s="7" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
     </row>
     <row r="54" spans="10:31" s="3" customFormat="1" ht="30" customHeight="1">
       <c r="J54" s="11" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="O54" s="11" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="P54" s="11" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="Q54" s="11" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="R54" s="11" t="s">
         <v>105</v>
@@ -6009,36 +6026,36 @@
       </c>
       <c r="W54" s="11"/>
       <c r="Y54" s="11" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="AA54" t="s">
         <v>39</v>
       </c>
       <c r="AB54" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="AC54" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="AD54" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="AE54" s="7" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
     </row>
     <row r="55" spans="10:31" s="3" customFormat="1" ht="30" customHeight="1">
       <c r="J55" s="11" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="O55" s="11" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P55" s="11" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="Q55" s="11" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="R55" s="11" t="s">
         <v>105</v>
@@ -6048,36 +6065,36 @@
       </c>
       <c r="W55" s="11"/>
       <c r="Y55" s="11" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="AA55" t="s">
         <v>39</v>
       </c>
       <c r="AB55" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="AC55" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="AD55" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="AE55" s="7" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
     </row>
     <row r="56" spans="10:31" s="3" customFormat="1" ht="30" customHeight="1">
       <c r="J56" s="11" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="O56" s="11" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="P56" s="11" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="Q56" s="11" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="R56" s="11" t="s">
         <v>105</v>
@@ -6087,36 +6104,36 @@
       </c>
       <c r="W56" s="11"/>
       <c r="Y56" s="11" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="AA56" t="s">
         <v>39</v>
       </c>
       <c r="AB56" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="AC56" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="AD56" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="AE56" s="7" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
     </row>
     <row r="57" spans="10:31" ht="30" customHeight="1">
       <c r="J57" s="5" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="O57" s="5" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="P57" s="5" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="Q57" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="R57" s="5" t="s">
         <v>105</v>
@@ -6126,36 +6143,36 @@
       </c>
       <c r="W57" s="5"/>
       <c r="Y57" s="5" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="AA57" t="s">
         <v>39</v>
       </c>
       <c r="AB57" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="AC57" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="AD57" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="AE57" s="7" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
     </row>
     <row r="58" spans="10:31" ht="30" customHeight="1">
       <c r="J58" s="5" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="O58" s="5" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="P58" s="5" t="s">
         <v>167</v>
       </c>
       <c r="Q58" s="5" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="R58" s="5" t="s">
         <v>169</v>
@@ -6165,36 +6182,36 @@
       </c>
       <c r="W58" s="5"/>
       <c r="Y58" s="5" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="AA58" t="s">
         <v>39</v>
       </c>
       <c r="AB58" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="AC58" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="AD58" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="AE58" s="7" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
     </row>
     <row r="59" spans="10:31" ht="30" customHeight="1">
       <c r="J59" s="5" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="O59" s="5" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="P59" s="5" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="Q59" s="5" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="R59" s="5" t="s">
         <v>169</v>
@@ -6204,36 +6221,36 @@
       </c>
       <c r="W59" s="5"/>
       <c r="Y59" s="5" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AA59" t="s">
         <v>39</v>
       </c>
       <c r="AB59" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="AC59" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="AD59" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="AE59" s="7" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
     </row>
     <row r="60" spans="10:31" ht="30" customHeight="1">
       <c r="J60" s="5" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="O60" s="5" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="P60" s="5" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="Q60" s="5" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="R60" s="5" t="s">
         <v>105</v>
@@ -6243,36 +6260,36 @@
       </c>
       <c r="W60" s="5"/>
       <c r="Y60" s="5" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="AA60" t="s">
         <v>39</v>
       </c>
       <c r="AB60" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="AC60" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AD60" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="AE60" s="7" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
     </row>
     <row r="61" spans="10:31" ht="30" customHeight="1">
       <c r="J61" s="5" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="O61" s="5" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="P61" s="5" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="Q61" s="5" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="R61" s="5" t="s">
         <v>169</v>
@@ -6282,36 +6299,36 @@
       </c>
       <c r="W61" s="5"/>
       <c r="Y61" s="5" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="AA61" t="s">
         <v>39</v>
       </c>
       <c r="AB61" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="AC61" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="AD61" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="AE61" s="7" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
     </row>
     <row r="62" spans="10:31" ht="30" customHeight="1">
       <c r="J62" s="5" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="O62" s="5" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="P62" s="5" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="Q62" s="5" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="R62" s="5" t="s">
         <v>105</v>
@@ -6321,36 +6338,36 @@
       </c>
       <c r="W62" s="5"/>
       <c r="Y62" s="5" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="AA62" t="s">
         <v>39</v>
       </c>
       <c r="AB62" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="AC62" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="AD62" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="AE62" s="7" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
     </row>
     <row r="63" spans="10:31" ht="30" customHeight="1">
       <c r="J63" s="5" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="O63" s="5" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="P63" s="5" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="Q63" s="5" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="R63" s="5" t="s">
         <v>47</v>
@@ -6360,36 +6377,36 @@
       </c>
       <c r="W63" s="5"/>
       <c r="Y63" s="5" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="AA63" t="s">
         <v>39</v>
       </c>
       <c r="AB63" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="AC63" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="AD63" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="AE63" s="7" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
     </row>
     <row r="64" spans="10:31" ht="30" customHeight="1">
       <c r="J64" s="5" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="O64" s="5" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="P64" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q64" s="5" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="R64" s="5" t="s">
         <v>105</v>
@@ -6399,27 +6416,27 @@
       </c>
       <c r="W64" s="5"/>
       <c r="Y64" s="5" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="AA64" t="s">
         <v>39</v>
       </c>
       <c r="AB64" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="AC64" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="AD64" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="AE64" s="7" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
     </row>
     <row r="65" spans="10:31" ht="30" customHeight="1">
       <c r="J65" s="5" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="O65" s="5" t="s">
         <v>224</v>
@@ -6428,7 +6445,7 @@
         <v>220</v>
       </c>
       <c r="Q65" s="5" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="R65" s="5" t="s">
         <v>169</v>
@@ -6438,7 +6455,7 @@
       </c>
       <c r="W65" s="5"/>
       <c r="Y65" s="5" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="AA65" t="s">
         <v>39</v>
@@ -6450,59 +6467,59 @@
         <v>224</v>
       </c>
       <c r="AD65" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="AE65" s="7" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="66" spans="10:31" ht="30" customHeight="1">
-      <c r="J66" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="O66" s="5" t="s">
-        <v>402</v>
-      </c>
-      <c r="P66" s="5" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="66" spans="10:31" s="15" customFormat="1" ht="30" customHeight="1">
+      <c r="J66" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="O66" s="19" t="s">
+        <v>393</v>
+      </c>
+      <c r="P66" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="Q66" s="5" t="s">
+      <c r="Q66" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="R66" s="5" t="s">
+      <c r="R66" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="V66" s="5" t="s">
+      <c r="V66" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="W66" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="Y66" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="AA66" t="s">
+      <c r="W66" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="Y66" s="19" t="s">
+        <v>583</v>
+      </c>
+      <c r="AA66" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="AD66" t="s">
-        <v>405</v>
-      </c>
-      <c r="AE66" s="7" t="s">
-        <v>406</v>
+      <c r="AD66" s="15" t="s">
+        <v>581</v>
+      </c>
+      <c r="AE66" s="23" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="67" spans="10:31" ht="30" customHeight="1">
       <c r="J67" s="5" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="O67" s="5" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="P67" s="5" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="Q67" s="5" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="R67" s="5" t="s">
         <v>169</v>
@@ -6512,30 +6529,30 @@
       </c>
       <c r="W67" s="5"/>
       <c r="Y67" s="5" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="AA67" t="s">
         <v>128</v>
       </c>
       <c r="AD67" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="AE67" s="7" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
     </row>
     <row r="68" spans="10:31" ht="30" customHeight="1">
       <c r="J68" s="5" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="O68" s="5" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="P68" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q68" s="5" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="R68" s="5" t="s">
         <v>105</v>
@@ -6545,36 +6562,36 @@
       </c>
       <c r="W68" s="5"/>
       <c r="Y68" s="5" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="AA68" t="s">
         <v>39</v>
       </c>
       <c r="AB68" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="AC68" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="AD68" t="s">
-        <v>418</v>
+        <v>584</v>
       </c>
       <c r="AE68" s="7" t="s">
-        <v>419</v>
+        <v>406</v>
       </c>
     </row>
     <row r="69" spans="10:31" ht="30" customHeight="1">
       <c r="J69" s="5" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="O69" s="5" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="P69" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q69" s="5" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="R69" s="5" t="s">
         <v>105</v>
@@ -6584,36 +6601,36 @@
       </c>
       <c r="W69" s="5"/>
       <c r="Y69" s="5" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="AA69" t="s">
         <v>39</v>
       </c>
       <c r="AB69" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="AC69" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="AD69" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="AE69" s="7" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
     </row>
     <row r="70" spans="10:31" ht="30" customHeight="1">
       <c r="J70" s="5" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="O70" s="5" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="P70" s="5" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="Q70" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="R70" s="5" t="s">
         <v>105</v>
@@ -6623,36 +6640,36 @@
       </c>
       <c r="W70" s="5"/>
       <c r="Y70" s="5" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="AA70" t="s">
         <v>39</v>
       </c>
       <c r="AB70" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="AC70" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="AD70" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="AE70" s="7" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
     </row>
     <row r="71" spans="10:31" ht="30" customHeight="1">
       <c r="J71" s="5" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="O71" s="5" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="P71" s="5" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="Q71" s="5" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="R71" s="5" t="s">
         <v>47</v>
@@ -6662,36 +6679,36 @@
       </c>
       <c r="W71" s="5"/>
       <c r="Y71" s="5" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="AA71" t="s">
         <v>39</v>
       </c>
       <c r="AB71" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="AC71" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="AD71" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="AE71" s="7" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
     </row>
     <row r="72" spans="10:31" ht="30" customHeight="1">
       <c r="J72" s="5" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="O72" s="5" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="P72" s="5" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="Q72" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="R72" s="5" t="s">
         <v>105</v>
@@ -6701,36 +6718,36 @@
       </c>
       <c r="W72" s="5"/>
       <c r="Y72" s="5" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="AA72" t="s">
         <v>39</v>
       </c>
       <c r="AB72" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="AC72" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="AD72" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="AE72" s="7" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
     </row>
     <row r="73" spans="10:31" ht="30" customHeight="1">
       <c r="J73" s="5" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="O73" s="5" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="P73" s="5" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="Q73" s="5" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="R73" s="5" t="s">
         <v>47</v>
@@ -6740,36 +6757,36 @@
       </c>
       <c r="W73" s="5"/>
       <c r="Y73" s="5" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="AA73" t="s">
         <v>111</v>
       </c>
       <c r="AB73" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="AC73" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="AD73" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="AE73" s="7" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
     </row>
     <row r="74" spans="10:31" ht="30" customHeight="1">
       <c r="J74" s="5" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="O74" s="5" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="P74" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q74" s="5" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="R74" s="5" t="s">
         <v>105</v>
@@ -6779,36 +6796,36 @@
       </c>
       <c r="W74" s="5"/>
       <c r="Y74" s="5" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="AA74" t="s">
         <v>111</v>
       </c>
       <c r="AB74" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="AC74" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="AD74" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="AE74" s="7" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
     </row>
     <row r="75" spans="10:31" ht="30" customHeight="1">
       <c r="J75" s="5" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="O75" s="5" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="P75" s="5" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="Q75" s="5" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="R75" s="5" t="s">
         <v>169</v>
@@ -6818,30 +6835,30 @@
       </c>
       <c r="W75" s="5"/>
       <c r="Y75" s="5" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="AA75" t="s">
         <v>128</v>
       </c>
       <c r="AD75" t="s">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="AE75" s="7" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
     </row>
     <row r="76" spans="10:31" ht="30" customHeight="1">
       <c r="J76" s="5" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="O76" s="5" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="P76" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q76" s="5" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="R76" s="5" t="s">
         <v>105</v>
@@ -6851,33 +6868,33 @@
       </c>
       <c r="W76" s="5"/>
       <c r="Y76" s="5" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="AA76" t="s">
         <v>39</v>
       </c>
       <c r="AB76" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="AC76" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="AD76" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="AE76" s="7" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
     </row>
     <row r="77" spans="10:31" ht="30" customHeight="1">
       <c r="J77" s="5" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="O77" s="5" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="P77" s="5" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="Q77" s="5" t="s">
         <v>62</v>
@@ -6890,30 +6907,30 @@
       </c>
       <c r="W77" s="5"/>
       <c r="Y77" s="5" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="AA77" t="s">
         <v>111</v>
       </c>
       <c r="AB77" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="AC77" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="AD77" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="AE77" s="7" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
     </row>
     <row r="78" spans="10:31" ht="30" customHeight="1">
       <c r="J78" s="5" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="O78" s="5" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="P78" s="5" t="s">
         <v>207</v>
@@ -6928,18 +6945,18 @@
         <v>56</v>
       </c>
       <c r="W78" s="5" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="Y78" s="5" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
     </row>
     <row r="79" spans="10:31" ht="30" customHeight="1">
       <c r="J79" s="5" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="O79" s="5" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="P79" s="5" t="s">
         <v>207</v>
@@ -6954,24 +6971,24 @@
         <v>56</v>
       </c>
       <c r="W79" s="5" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="Y79" s="5" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
     </row>
     <row r="80" spans="10:31" ht="30" customHeight="1">
       <c r="J80" s="5" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="O80" s="5" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="P80" s="5" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="Q80" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="R80" s="5" t="s">
         <v>105</v>
@@ -6981,36 +6998,36 @@
       </c>
       <c r="W80" s="5"/>
       <c r="Y80" s="5" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="AA80" t="s">
         <v>39</v>
       </c>
       <c r="AB80" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="AC80" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="AD80" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="AE80" s="7" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
     </row>
     <row r="81" spans="10:31" ht="30" customHeight="1">
       <c r="J81" s="5" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="O81" s="5" t="s">
-        <v>482</v>
+        <v>469</v>
       </c>
       <c r="P81" s="5" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="Q81" s="5" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="R81" s="5" t="s">
         <v>47</v>
@@ -7020,36 +7037,36 @@
       </c>
       <c r="W81" s="5"/>
       <c r="Y81" s="5" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="AA81" t="s">
         <v>39</v>
       </c>
       <c r="AB81" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="AC81" t="s">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="AD81" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="AE81" s="7" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
     </row>
     <row r="82" spans="10:31" ht="30" customHeight="1">
       <c r="J82" s="5" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="O82" s="5" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="P82" s="5" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="Q82" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="R82" s="5" t="s">
         <v>169</v>
@@ -7059,36 +7076,36 @@
       </c>
       <c r="W82" s="5"/>
       <c r="Y82" s="5" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="AA82" t="s">
         <v>111</v>
       </c>
       <c r="AB82" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="AC82" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="AD82" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="AE82" s="7" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
     </row>
     <row r="83" spans="10:31" ht="30" customHeight="1">
       <c r="J83" s="5" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="O83" s="5" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="P83" s="5" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="Q83" s="5" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="R83" s="5" t="s">
         <v>47</v>
@@ -7098,36 +7115,36 @@
       </c>
       <c r="W83" s="5"/>
       <c r="Y83" s="5" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="AA83" t="s">
         <v>39</v>
       </c>
       <c r="AB83" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="AC83" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="AD83" t="s">
-        <v>494</v>
+        <v>481</v>
       </c>
       <c r="AE83" s="7" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
     </row>
     <row r="84" spans="10:31" ht="30" customHeight="1">
       <c r="J84" s="5" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="O84" s="5" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="P84" s="5" t="s">
         <v>67</v>
       </c>
       <c r="Q84" s="5" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="R84" s="5" t="s">
         <v>55</v>
@@ -7136,39 +7153,39 @@
         <v>56</v>
       </c>
       <c r="W84" s="5" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="Y84" s="5" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="AA84" t="s">
         <v>39</v>
       </c>
       <c r="AB84" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="AC84" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="AD84" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="AE84" s="7" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
     </row>
     <row r="85" spans="10:31" ht="30" customHeight="1">
       <c r="J85" s="5" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="O85" s="5" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
       <c r="P85" s="5" t="s">
         <v>67</v>
       </c>
       <c r="Q85" s="5" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="R85" s="5" t="s">
         <v>55</v>
@@ -7177,39 +7194,39 @@
         <v>56</v>
       </c>
       <c r="W85" s="5" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="Y85" s="5" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="AA85" t="s">
         <v>111</v>
       </c>
       <c r="AB85" t="s">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="AC85" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="AD85" t="s">
-        <v>508</v>
+        <v>495</v>
       </c>
       <c r="AE85" s="7" t="s">
-        <v>509</v>
+        <v>496</v>
       </c>
     </row>
     <row r="86" spans="10:31" ht="30" customHeight="1">
       <c r="J86" s="5" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="O86" s="5" t="s">
-        <v>510</v>
+        <v>497</v>
       </c>
       <c r="P86" s="5" t="s">
         <v>67</v>
       </c>
       <c r="Q86" s="5" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="R86" s="5" t="s">
         <v>55</v>
@@ -7218,39 +7235,39 @@
         <v>56</v>
       </c>
       <c r="W86" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="Y86" s="5" t="s">
         <v>498</v>
-      </c>
-      <c r="Y86" s="5" t="s">
-        <v>511</v>
       </c>
       <c r="AA86" t="s">
         <v>111</v>
       </c>
       <c r="AB86" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="AC86" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="AD86" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="AE86" s="7" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
     </row>
     <row r="87" spans="10:31" ht="30" customHeight="1">
       <c r="J87" s="5" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="O87" s="5" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="P87" s="5" t="s">
         <v>214</v>
       </c>
       <c r="Q87" s="5" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="R87" s="5" t="s">
         <v>169</v>
@@ -7260,30 +7277,30 @@
       </c>
       <c r="W87" s="5"/>
       <c r="Y87" s="5" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="AA87" t="s">
         <v>128</v>
       </c>
       <c r="AD87" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
       <c r="AE87" s="7" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
     </row>
     <row r="88" spans="10:31" ht="30" customHeight="1">
       <c r="J88" s="5" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="O88" s="5" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="P88" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q88" s="5" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="R88" s="5" t="s">
         <v>105</v>
@@ -7293,30 +7310,30 @@
       </c>
       <c r="W88" s="5"/>
       <c r="Y88" s="5" t="s">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="AA88" t="s">
         <v>128</v>
       </c>
       <c r="AD88" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="AE88" s="7" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
     </row>
     <row r="89" spans="10:31" ht="30" customHeight="1">
       <c r="J89" s="5" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="O89" s="5" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="P89" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q89" s="5" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="R89" s="5" t="s">
         <v>105</v>
@@ -7326,36 +7343,36 @@
       </c>
       <c r="W89" s="5"/>
       <c r="Y89" s="5" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="AA89" t="s">
         <v>39</v>
       </c>
       <c r="AB89" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="AC89" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="AD89" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="AE89" s="7" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
     </row>
     <row r="90" spans="10:31" ht="30" customHeight="1">
       <c r="J90" s="5" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="O90" s="5" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="P90" s="5" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="Q90" s="5" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="R90" s="5" t="s">
         <v>169</v>
@@ -7365,30 +7382,30 @@
       </c>
       <c r="W90" s="5"/>
       <c r="Y90" s="5" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="AA90" t="s">
         <v>128</v>
       </c>
       <c r="AD90" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
       <c r="AE90" s="7" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
     </row>
     <row r="91" spans="10:31" ht="30" customHeight="1">
       <c r="J91" s="5" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="O91" s="5" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="P91" s="5" t="s">
-        <v>530</v>
+        <v>517</v>
       </c>
       <c r="Q91" s="5" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="R91" s="5" t="s">
         <v>169</v>
@@ -7398,30 +7415,30 @@
       </c>
       <c r="W91" s="5"/>
       <c r="Y91" s="5" t="s">
-        <v>531</v>
+        <v>518</v>
       </c>
       <c r="AA91" t="s">
         <v>39</v>
       </c>
       <c r="AB91" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="AC91" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="AD91" t="s">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="AE91" s="7" t="s">
-        <v>534</v>
+        <v>521</v>
       </c>
     </row>
     <row r="92" spans="10:31" ht="30" customHeight="1">
       <c r="J92" s="5" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="O92" s="5" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="P92" s="5" t="s">
         <v>207</v>
@@ -7436,24 +7453,24 @@
         <v>56</v>
       </c>
       <c r="W92" s="5" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="Y92" s="5" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
     </row>
     <row r="93" spans="10:31" ht="30" customHeight="1">
       <c r="J93" s="5" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="O93" s="5" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="P93" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q93" s="5" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="R93" s="5" t="s">
         <v>105</v>
@@ -7463,30 +7480,30 @@
       </c>
       <c r="W93" s="5"/>
       <c r="Y93" s="5" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="AA93" t="s">
         <v>39</v>
       </c>
       <c r="AB93" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="AC93" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="AD93" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="AE93" s="7" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
     </row>
     <row r="94" spans="10:31" ht="30" customHeight="1">
       <c r="J94" s="5" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="O94" s="5" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="P94" s="5" t="s">
         <v>207</v>
@@ -7501,21 +7518,21 @@
         <v>56</v>
       </c>
       <c r="W94" s="5" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="Y94" s="5" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
     </row>
     <row r="95" spans="10:31" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="J95" s="12" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="O95" s="12" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
       <c r="P95" s="12" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="Q95" s="10">
         <v>10</v>
@@ -7527,33 +7544,33 @@
         <v>38</v>
       </c>
       <c r="Y95" s="12" t="s">
-        <v>540</v>
+        <v>527</v>
       </c>
       <c r="AA95" t="s">
         <v>111</v>
       </c>
       <c r="AB95" t="s">
-        <v>541</v>
+        <v>528</v>
       </c>
       <c r="AC95" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="AD95" t="s">
-        <v>543</v>
+        <v>530</v>
       </c>
       <c r="AE95" s="7" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
     </row>
     <row r="96" spans="10:31" ht="15" customHeight="1">
       <c r="J96" s="13" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="O96" s="13" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
       <c r="P96" s="13" t="s">
-        <v>546</v>
+        <v>533</v>
       </c>
       <c r="Q96" s="6">
         <v>1228</v>
@@ -7565,33 +7582,33 @@
         <v>38</v>
       </c>
       <c r="Y96" s="13" t="s">
-        <v>547</v>
+        <v>534</v>
       </c>
       <c r="AA96" t="s">
         <v>111</v>
       </c>
       <c r="AB96" t="s">
-        <v>548</v>
+        <v>535</v>
       </c>
       <c r="AC96" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="AD96" t="s">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="AE96" s="7" t="s">
-        <v>551</v>
+        <v>538</v>
       </c>
     </row>
     <row r="97" spans="10:31" ht="30" customHeight="1">
       <c r="J97" s="13" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="O97" s="13" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="P97" s="13" t="s">
-        <v>546</v>
+        <v>533</v>
       </c>
       <c r="Q97" s="6">
         <v>10</v>
@@ -7603,24 +7620,24 @@
         <v>38</v>
       </c>
       <c r="Y97" s="13" t="s">
-        <v>553</v>
+        <v>540</v>
       </c>
       <c r="AA97" t="s">
         <v>128</v>
       </c>
       <c r="AD97" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="AE97" s="7" t="s">
-        <v>555</v>
+        <v>542</v>
       </c>
     </row>
     <row r="98" spans="10:31" ht="28.8" customHeight="1">
       <c r="J98" s="13" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="O98" s="13" t="s">
-        <v>556</v>
+        <v>543</v>
       </c>
       <c r="P98" s="13" t="s">
         <v>53</v>
@@ -7635,21 +7652,21 @@
         <v>56</v>
       </c>
       <c r="W98" t="s">
-        <v>557</v>
+        <v>544</v>
       </c>
       <c r="Y98" s="13" t="s">
-        <v>558</v>
+        <v>545</v>
       </c>
     </row>
     <row r="99" spans="10:31" ht="15" customHeight="1">
       <c r="J99" s="13" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="O99" s="13" t="s">
-        <v>559</v>
+        <v>546</v>
       </c>
       <c r="P99" s="13" t="s">
-        <v>546</v>
+        <v>533</v>
       </c>
       <c r="Q99" s="6">
         <v>1228</v>
@@ -7661,36 +7678,36 @@
         <v>38</v>
       </c>
       <c r="Y99" s="13" t="s">
-        <v>560</v>
+        <v>547</v>
       </c>
       <c r="AA99" t="s">
         <v>111</v>
       </c>
       <c r="AB99" t="s">
-        <v>561</v>
+        <v>548</v>
       </c>
       <c r="AC99" t="s">
-        <v>559</v>
+        <v>546</v>
       </c>
       <c r="AD99" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="AE99" s="7" t="s">
-        <v>563</v>
+        <v>550</v>
       </c>
     </row>
     <row r="100" spans="10:31" ht="15" customHeight="1">
       <c r="J100" s="13" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="O100" s="13" t="s">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="P100" s="13" t="s">
         <v>45</v>
       </c>
       <c r="Q100" s="14" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="R100" s="13" t="s">
         <v>47</v>
@@ -7699,33 +7716,33 @@
         <v>38</v>
       </c>
       <c r="Y100" s="13" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="AA100" t="s">
         <v>111</v>
       </c>
       <c r="AB100" t="s">
-        <v>567</v>
+        <v>554</v>
       </c>
       <c r="AC100" t="s">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="AD100" t="s">
-        <v>568</v>
+        <v>555</v>
       </c>
       <c r="AE100" s="7" t="s">
-        <v>569</v>
+        <v>556</v>
       </c>
     </row>
     <row r="101" spans="10:31" ht="30" customHeight="1">
       <c r="J101" s="13" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="O101" s="13" t="s">
-        <v>570</v>
+        <v>557</v>
       </c>
       <c r="P101" s="13" t="s">
-        <v>546</v>
+        <v>533</v>
       </c>
       <c r="Q101" s="6">
         <v>1228</v>
@@ -7737,33 +7754,33 @@
         <v>38</v>
       </c>
       <c r="Y101" s="13" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="AA101" t="s">
         <v>111</v>
       </c>
       <c r="AB101" t="s">
-        <v>548</v>
+        <v>535</v>
       </c>
       <c r="AC101" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="AD101" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="AE101" s="7" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
     </row>
     <row r="102" spans="10:31" ht="30" customHeight="1">
       <c r="J102" s="13" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="O102" s="13" t="s">
-        <v>574</v>
+        <v>561</v>
       </c>
       <c r="P102" s="13" t="s">
-        <v>546</v>
+        <v>533</v>
       </c>
       <c r="Q102" s="6">
         <v>10</v>
@@ -7775,16 +7792,16 @@
         <v>38</v>
       </c>
       <c r="Y102" s="13" t="s">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="AA102" t="s">
         <v>128</v>
       </c>
       <c r="AD102" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="AE102" s="7" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
     </row>
     <row r="103" spans="10:31" ht="15" customHeight="1"/>
@@ -8063,6 +8080,6 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>